--- a/Interview Test P1.xlsx
+++ b/Interview Test P1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaloyan\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6790E87D-8E8D-4FB1-A099-81D16FC463AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132D9641-AD1D-435F-932A-5B09C0413EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2235" windowWidth="23535" windowHeight="13035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="1770" windowWidth="23535" windowHeight="13035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -454,13 +454,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="25.42578125" customWidth="1"/>
     <col min="4" max="4" width="43.5703125" customWidth="1"/>
     <col min="5" max="5" width="41.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="16384" width="12.5703125" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">

--- a/Interview Test P1.xlsx
+++ b/Interview Test P1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132D9641-AD1D-435F-932A-5B09C0413EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="1770" windowWidth="23535" windowHeight="13035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
